--- a/marebuis_vol2.1_m.xlsx
+++ b/marebuis_vol2.1_m.xlsx
@@ -1,14 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c281a82ac62a8fe2/デスクトップ/研究Ongo/MareBuis/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="814" documentId="11_1147F767884006CC70C5DF64F5012D16E1073E97" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAF20130-894F-4A64-A178-50D73E83D1F4}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="815" documentId="11_1147F767884006CC70C5DF64F5012D16E1073E97" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F718F4B-9618-4EEE-8B4A-619B66C02697}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +30,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -18740,7 +18735,8 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -20603,6 +20599,7 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -23251,6 +23248,7 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>